--- a/excel/Mac快捷键总表.xlsx
+++ b/excel/Mac快捷键总表.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DEB3AF-4C84-4568-BD4C-3D9DB8481F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="328">
   <si>
     <t>快捷键组合</t>
   </si>
@@ -1003,13 +1004,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1036,15 +1043,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{90DB5370-1D7F-4BE2-B4B7-81C38436440E}" name="表1" displayName="表1" ref="A1:D117" totalsRowShown="0">
+  <autoFilter ref="A1:D117" xr:uid="{90DB5370-1D7F-4BE2-B4B7-81C38436440E}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{4A37AAB5-B0C7-4F53-A0A8-114F6E7D7487}" name="快捷键组合"/>
+    <tableColumn id="2" xr3:uid="{803857A9-245B-414D-93EC-CCD125225E57}" name="功能描述"/>
+    <tableColumn id="3" xr3:uid="{B58F6F3B-8391-45F7-A2A8-60B2FBE8CAFC}" name="适用场景"/>
+    <tableColumn id="4" xr3:uid="{EA7DDFDB-70C4-4627-99B1-28A9D16A07CE}" name="所属分类"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1300,17 +1333,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D117"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="36"/>
-    <col customWidth="true" max="3" min="3" width="12"/>
-    <col customWidth="true" max="4" min="4" width="46"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="63.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1318,13 +1351,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1338,7 +1371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1346,13 +1379,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1360,13 +1393,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1374,13 +1407,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1388,13 +1421,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1402,13 +1435,13 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1416,13 +1449,13 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1430,13 +1463,13 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1444,13 +1477,13 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1458,13 +1491,13 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1472,13 +1505,13 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13">
+    </row>
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1486,13 +1519,13 @@
         <v>38</v>
       </c>
       <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1500,13 +1533,13 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1514,13 +1547,13 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
         <v>42</v>
       </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1528,13 +1561,13 @@
         <v>48</v>
       </c>
       <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1548,7 +1581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1556,13 +1589,13 @@
         <v>52</v>
       </c>
       <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
         <v>53</v>
       </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19">
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1570,13 +1603,13 @@
         <v>56</v>
       </c>
       <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
         <v>53</v>
       </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -1584,13 +1617,13 @@
         <v>59</v>
       </c>
       <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21">
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -1598,13 +1631,13 @@
         <v>63</v>
       </c>
       <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
         <v>53</v>
       </c>
-      <c r="D21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22">
+    </row>
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -1612,13 +1645,13 @@
         <v>66</v>
       </c>
       <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23">
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1626,13 +1659,13 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
         <v>53</v>
       </c>
-      <c r="D23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24">
+    </row>
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -1640,13 +1673,13 @@
         <v>72</v>
       </c>
       <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
         <v>53</v>
       </c>
-      <c r="D24" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25">
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -1654,13 +1687,13 @@
         <v>75</v>
       </c>
       <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
         <v>76</v>
       </c>
-      <c r="D25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26">
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -1668,13 +1701,13 @@
         <v>79</v>
       </c>
       <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
         <v>80</v>
       </c>
-      <c r="D26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27">
+    </row>
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -1682,13 +1715,13 @@
         <v>83</v>
       </c>
       <c r="C27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" t="s">
         <v>53</v>
       </c>
-      <c r="D27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28">
+    </row>
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -1696,13 +1729,13 @@
         <v>86</v>
       </c>
       <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
       </c>
-      <c r="D28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29">
+    </row>
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>89</v>
       </c>
@@ -1716,7 +1749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -1724,13 +1757,13 @@
         <v>91</v>
       </c>
       <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
         <v>92</v>
       </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -1738,13 +1771,13 @@
         <v>95</v>
       </c>
       <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
         <v>92</v>
       </c>
-      <c r="D31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32">
+    </row>
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -1752,13 +1785,13 @@
         <v>98</v>
       </c>
       <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
         <v>92</v>
       </c>
-      <c r="D32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33">
+    </row>
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>100</v>
       </c>
@@ -1766,13 +1799,13 @@
         <v>101</v>
       </c>
       <c r="C33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" t="s">
         <v>92</v>
       </c>
-      <c r="D33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34">
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>103</v>
       </c>
@@ -1780,13 +1813,13 @@
         <v>104</v>
       </c>
       <c r="C34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" t="s">
         <v>105</v>
       </c>
-      <c r="D34" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35">
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -1794,13 +1827,13 @@
         <v>108</v>
       </c>
       <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
         <v>105</v>
       </c>
-      <c r="D35" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -1808,13 +1841,13 @@
         <v>111</v>
       </c>
       <c r="C36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" t="s">
         <v>92</v>
       </c>
-      <c r="D36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37">
+    </row>
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>113</v>
       </c>
@@ -1822,13 +1855,13 @@
         <v>114</v>
       </c>
       <c r="C37" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" t="s">
         <v>92</v>
       </c>
-      <c r="D37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38">
+    </row>
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>116</v>
       </c>
@@ -1836,13 +1869,13 @@
         <v>117</v>
       </c>
       <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" t="s">
         <v>42</v>
       </c>
-      <c r="D38" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39">
+    </row>
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>119</v>
       </c>
@@ -1850,13 +1883,13 @@
         <v>120</v>
       </c>
       <c r="C39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" t="s">
         <v>92</v>
       </c>
-      <c r="D39" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -1864,13 +1897,13 @@
         <v>123</v>
       </c>
       <c r="C40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" t="s">
         <v>92</v>
       </c>
-      <c r="D40" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41">
+    </row>
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>125</v>
       </c>
@@ -1878,13 +1911,13 @@
         <v>126</v>
       </c>
       <c r="C41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" t="s">
         <v>92</v>
       </c>
-      <c r="D41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42">
+    </row>
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>128</v>
       </c>
@@ -1898,7 +1931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -1906,13 +1939,13 @@
         <v>130</v>
       </c>
       <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" t="s">
         <v>131</v>
       </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>133</v>
       </c>
@@ -1920,13 +1953,13 @@
         <v>134</v>
       </c>
       <c r="C44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" t="s">
         <v>131</v>
       </c>
-      <c r="D44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>136</v>
       </c>
@@ -1934,13 +1967,13 @@
         <v>137</v>
       </c>
       <c r="C45" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" t="s">
         <v>138</v>
       </c>
-      <c r="D45" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46">
+    </row>
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>140</v>
       </c>
@@ -1948,13 +1981,13 @@
         <v>141</v>
       </c>
       <c r="C46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" t="s">
         <v>142</v>
       </c>
-      <c r="D46" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -1962,13 +1995,13 @@
         <v>145</v>
       </c>
       <c r="C47" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" t="s">
         <v>146</v>
       </c>
-      <c r="D47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48">
+    </row>
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -1976,13 +2009,13 @@
         <v>149</v>
       </c>
       <c r="C48" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" t="s">
         <v>150</v>
       </c>
-      <c r="D48" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -1996,7 +2029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>153</v>
       </c>
@@ -2004,13 +2037,13 @@
         <v>154</v>
       </c>
       <c r="C50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" t="s">
         <v>155</v>
       </c>
-      <c r="D50" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2018,13 +2051,13 @@
         <v>158</v>
       </c>
       <c r="C51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" t="s">
         <v>155</v>
       </c>
-      <c r="D51" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -2032,13 +2065,13 @@
         <v>161</v>
       </c>
       <c r="C52" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" t="s">
         <v>155</v>
       </c>
-      <c r="D52" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53">
+    </row>
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -2052,7 +2085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>164</v>
       </c>
@@ -2060,13 +2093,13 @@
         <v>165</v>
       </c>
       <c r="C54" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" t="s">
         <v>166</v>
       </c>
-      <c r="D54" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>168</v>
       </c>
@@ -2074,13 +2107,13 @@
         <v>169</v>
       </c>
       <c r="C55" t="s">
+        <v>170</v>
+      </c>
+      <c r="D55" t="s">
         <v>166</v>
       </c>
-      <c r="D55" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>171</v>
       </c>
@@ -2088,13 +2121,13 @@
         <v>172</v>
       </c>
       <c r="C56" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" t="s">
         <v>166</v>
       </c>
-      <c r="D56" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>174</v>
       </c>
@@ -2102,13 +2135,13 @@
         <v>175</v>
       </c>
       <c r="C57" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" t="s">
         <v>166</v>
       </c>
-      <c r="D57" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="58">
+    </row>
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>177</v>
       </c>
@@ -2122,7 +2155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>178</v>
       </c>
@@ -2130,13 +2163,13 @@
         <v>179</v>
       </c>
       <c r="C59" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>182</v>
       </c>
@@ -2144,13 +2177,13 @@
         <v>183</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D60" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>100</v>
       </c>
@@ -2158,13 +2191,13 @@
         <v>185</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D61" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>187</v>
       </c>
@@ -2172,13 +2205,13 @@
         <v>188</v>
       </c>
       <c r="C62" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D62" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>190</v>
       </c>
@@ -2186,13 +2219,13 @@
         <v>191</v>
       </c>
       <c r="C63" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -2200,13 +2233,13 @@
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D64" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>194</v>
       </c>
@@ -2214,13 +2247,13 @@
         <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -2228,13 +2261,13 @@
         <v>198</v>
       </c>
       <c r="C66" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="D66" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -2242,13 +2275,13 @@
         <v>29</v>
       </c>
       <c r="C67" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>31</v>
       </c>
@@ -2256,13 +2289,13 @@
         <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="D68" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>201</v>
       </c>
@@ -2270,13 +2303,13 @@
         <v>202</v>
       </c>
       <c r="C69" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D69" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>204</v>
       </c>
@@ -2284,13 +2317,13 @@
         <v>205</v>
       </c>
       <c r="C70" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="D70" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>207</v>
       </c>
@@ -2298,13 +2331,13 @@
         <v>208</v>
       </c>
       <c r="C71" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="D71" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>113</v>
       </c>
@@ -2312,13 +2345,13 @@
         <v>210</v>
       </c>
       <c r="C72" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="D72" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>212</v>
       </c>
@@ -2326,13 +2359,13 @@
         <v>213</v>
       </c>
       <c r="C73" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D73" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>68</v>
       </c>
@@ -2340,13 +2373,13 @@
         <v>215</v>
       </c>
       <c r="C74" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="D74" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>71</v>
       </c>
@@ -2354,13 +2387,13 @@
         <v>72</v>
       </c>
       <c r="C75" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="D75" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>218</v>
       </c>
@@ -2368,13 +2401,13 @@
         <v>219</v>
       </c>
       <c r="C76" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="D76" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>90</v>
       </c>
@@ -2382,13 +2415,13 @@
         <v>221</v>
       </c>
       <c r="C77" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="D77" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -2396,13 +2429,13 @@
         <v>223</v>
       </c>
       <c r="C78" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="D78" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>37</v>
       </c>
@@ -2410,13 +2443,13 @@
         <v>225</v>
       </c>
       <c r="C79" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="D79" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>58</v>
       </c>
@@ -2424,13 +2457,13 @@
         <v>227</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="D80" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>229</v>
       </c>
@@ -2438,13 +2471,13 @@
         <v>230</v>
       </c>
       <c r="C81" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="D81" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>232</v>
       </c>
@@ -2452,13 +2485,13 @@
         <v>233</v>
       </c>
       <c r="C82" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="D82" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -2466,13 +2499,13 @@
         <v>235</v>
       </c>
       <c r="C83" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="D83" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -2480,13 +2513,13 @@
         <v>237</v>
       </c>
       <c r="C84" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="D84" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>239</v>
       </c>
@@ -2494,13 +2527,13 @@
         <v>240</v>
       </c>
       <c r="C85" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="D85" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>242</v>
       </c>
@@ -2508,13 +2541,13 @@
         <v>243</v>
       </c>
       <c r="C86" t="s">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>245</v>
       </c>
@@ -2522,13 +2555,13 @@
         <v>246</v>
       </c>
       <c r="C87" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="D87" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>51</v>
       </c>
@@ -2536,13 +2569,13 @@
         <v>248</v>
       </c>
       <c r="C88" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="D88" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>250</v>
       </c>
@@ -2550,13 +2583,13 @@
         <v>251</v>
       </c>
       <c r="C89" t="s">
-        <v>180</v>
+        <v>252</v>
       </c>
       <c r="D89" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>253</v>
       </c>
@@ -2564,13 +2597,13 @@
         <v>254</v>
       </c>
       <c r="C90" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="D90" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>256</v>
       </c>
@@ -2578,13 +2611,13 @@
         <v>257</v>
       </c>
       <c r="C91" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="D91" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>259</v>
       </c>
@@ -2592,13 +2625,13 @@
         <v>260</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="D92" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -2606,13 +2639,13 @@
         <v>263</v>
       </c>
       <c r="C93" t="s">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>265</v>
       </c>
@@ -2620,13 +2653,13 @@
         <v>266</v>
       </c>
       <c r="C94" t="s">
+        <v>267</v>
+      </c>
+      <c r="D94" t="s">
         <v>8</v>
       </c>
-      <c r="D94" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>268</v>
       </c>
@@ -2634,13 +2667,13 @@
         <v>269</v>
       </c>
       <c r="C95" t="s">
+        <v>267</v>
+      </c>
+      <c r="D95" t="s">
         <v>8</v>
       </c>
-      <c r="D95" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="96">
+    </row>
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>103</v>
       </c>
@@ -2648,13 +2681,13 @@
         <v>270</v>
       </c>
       <c r="C96" t="s">
+        <v>271</v>
+      </c>
+      <c r="D96" t="s">
         <v>8</v>
       </c>
-      <c r="D96" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>272</v>
       </c>
@@ -2662,13 +2695,13 @@
         <v>273</v>
       </c>
       <c r="C97" t="s">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="D97" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -2676,13 +2709,13 @@
         <v>275</v>
       </c>
       <c r="C98" t="s">
-        <v>180</v>
+        <v>276</v>
       </c>
       <c r="D98" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>277</v>
       </c>
@@ -2690,13 +2723,13 @@
         <v>278</v>
       </c>
       <c r="C99" t="s">
-        <v>180</v>
+        <v>279</v>
       </c>
       <c r="D99" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>280</v>
       </c>
@@ -2704,13 +2737,13 @@
         <v>281</v>
       </c>
       <c r="C100" t="s">
-        <v>180</v>
+        <v>282</v>
       </c>
       <c r="D100" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>283</v>
       </c>
@@ -2718,13 +2751,13 @@
         <v>284</v>
       </c>
       <c r="C101" t="s">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="D101" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>286</v>
       </c>
@@ -2732,13 +2765,13 @@
         <v>287</v>
       </c>
       <c r="C102" t="s">
-        <v>180</v>
+        <v>288</v>
       </c>
       <c r="D102" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>289</v>
       </c>
@@ -2746,13 +2779,13 @@
         <v>290</v>
       </c>
       <c r="C103" t="s">
-        <v>180</v>
+        <v>288</v>
       </c>
       <c r="D103" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>291</v>
       </c>
@@ -2760,13 +2793,13 @@
         <v>292</v>
       </c>
       <c r="C104" t="s">
-        <v>180</v>
+        <v>293</v>
       </c>
       <c r="D104" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>294</v>
       </c>
@@ -2774,13 +2807,13 @@
         <v>295</v>
       </c>
       <c r="C105" t="s">
-        <v>180</v>
+        <v>296</v>
       </c>
       <c r="D105" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>297</v>
       </c>
@@ -2788,13 +2821,13 @@
         <v>298</v>
       </c>
       <c r="C106" t="s">
-        <v>180</v>
+        <v>299</v>
       </c>
       <c r="D106" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>300</v>
       </c>
@@ -2802,13 +2835,13 @@
         <v>301</v>
       </c>
       <c r="C107" t="s">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="D107" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>303</v>
       </c>
@@ -2816,13 +2849,13 @@
         <v>304</v>
       </c>
       <c r="C108" t="s">
-        <v>180</v>
+        <v>305</v>
       </c>
       <c r="D108" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>306</v>
       </c>
@@ -2830,13 +2863,13 @@
         <v>307</v>
       </c>
       <c r="C109" t="s">
-        <v>180</v>
+        <v>308</v>
       </c>
       <c r="D109" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>309</v>
       </c>
@@ -2844,13 +2877,13 @@
         <v>310</v>
       </c>
       <c r="C110" t="s">
-        <v>180</v>
+        <v>311</v>
       </c>
       <c r="D110" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>312</v>
       </c>
@@ -2858,13 +2891,13 @@
         <v>313</v>
       </c>
       <c r="C111" t="s">
-        <v>180</v>
+        <v>314</v>
       </c>
       <c r="D111" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>148</v>
       </c>
@@ -2872,13 +2905,13 @@
         <v>315</v>
       </c>
       <c r="C112" t="s">
-        <v>180</v>
+        <v>316</v>
       </c>
       <c r="D112" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>317</v>
       </c>
@@ -2886,13 +2919,13 @@
         <v>318</v>
       </c>
       <c r="C113" t="s">
-        <v>180</v>
+        <v>319</v>
       </c>
       <c r="D113" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>320</v>
       </c>
@@ -2900,13 +2933,13 @@
         <v>321</v>
       </c>
       <c r="C114" t="s">
-        <v>180</v>
+        <v>322</v>
       </c>
       <c r="D114" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>323</v>
       </c>
@@ -2914,13 +2947,13 @@
         <v>324</v>
       </c>
       <c r="C115" t="s">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="D115" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>74</v>
       </c>
@@ -2928,13 +2961,13 @@
         <v>298</v>
       </c>
       <c r="C116" t="s">
-        <v>180</v>
+        <v>326</v>
       </c>
       <c r="D116" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>327</v>
       </c>
@@ -2942,12 +2975,17 @@
         <v>301</v>
       </c>
       <c r="C117" t="s">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="D117" t="s">
-        <v>302</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>